--- a/VerveStacks_POL_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{756D2AF3-CA6F-402C-8E15-5898536A9A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02EFED1B-93DF-42B6-9D45-D1C2FB674341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C2E46BF-9678-4A05-B138-ABBFD4E35AD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{05ACF715-216B-4043-9ED9-243A3D65A2E5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -604,7 +604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FABDDA8-E0E7-4687-93C5-F61B6860554E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F0C94B-7EDB-4315-8CE0-B242BBDD6EEB}">
   <dimension ref="B3:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
